--- a/sheets/대금율보/검수/대금산조 중중모리.xlsx
+++ b/sheets/대금율보/검수/대금산조 중중모리.xlsx
@@ -28617,7 +28617,7 @@
       <c r="I6" s="22"/>
       <c r="J6" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢?</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="K6" s="24" t="inlineStr">
@@ -28781,7 +28781,7 @@
       <c r="M9" s="22"/>
       <c r="N9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">南?</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="O9" s="24" t="inlineStr">
@@ -29291,7 +29291,7 @@
       <c r="O20" s="22"/>
       <c r="P20" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲?</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="Q20" s="24" t="inlineStr">
@@ -29607,7 +29607,7 @@
       <c r="A27" s="0"/>
       <c r="B27" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞?</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr">
@@ -29919,7 +29919,7 @@
       <c r="O33" s="22"/>
       <c r="P33" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">南?</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="Q33" s="24" t="inlineStr">
@@ -29999,7 +29999,7 @@
       <c r="A35" s="0"/>
       <c r="B35" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋?</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="C35" s="24" t="inlineStr">
@@ -30123,7 +30123,7 @@
       <c r="C37" s="22"/>
       <c r="D37" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋?</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="E37" s="24" t="inlineStr">
@@ -30299,7 +30299,7 @@
       <c r="O40" s="22"/>
       <c r="P40" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢?</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="Q40" s="24" t="inlineStr">
@@ -30484,7 +30484,7 @@
       <c r="F45" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-仲?</t>
+仲</t>
         </is>
       </c>
       <c r="G45" s="24" t="inlineStr">
@@ -30583,7 +30583,7 @@
       <c r="Q46" s="22"/>
       <c r="R46" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋?</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="S46" s="24" t="inlineStr">
@@ -30699,7 +30699,7 @@
       <c r="S48" s="22"/>
       <c r="T48" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋?</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="U48" s="24" t="inlineStr">
@@ -30756,7 +30756,7 @@
       <c r="Q49" s="22"/>
       <c r="R49" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋?</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="S49" s="24" t="inlineStr">
@@ -31022,7 +31022,7 @@
       <c r="S54" s="22"/>
       <c r="T54" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋?</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="U54" s="24" t="inlineStr">
@@ -31205,7 +31205,7 @@
       <c r="R59" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-仲?</t>
+仲</t>
         </is>
       </c>
       <c r="S59" s="24" t="inlineStr">
@@ -31359,7 +31359,7 @@
       <c r="C62" s="22"/>
       <c r="D62" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋?</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="E62" s="24" t="inlineStr">
@@ -31369,7 +31369,7 @@
       </c>
       <c r="F62" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋?</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="G62" s="24" t="inlineStr">
@@ -31697,7 +31697,7 @@
       <c r="C68" s="22"/>
       <c r="D68" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋?</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="E68" s="24" t="inlineStr">
@@ -31707,7 +31707,7 @@
       </c>
       <c r="F68" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋?</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="G68" s="24" t="inlineStr">
@@ -31920,7 +31920,7 @@
       <c r="K73" s="22"/>
       <c r="L73" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">林?</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="M73" s="24" t="inlineStr">
@@ -31937,7 +31937,7 @@
       <c r="P73" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-仲?</t>
+仲</t>
         </is>
       </c>
       <c r="Q73" s="24" t="inlineStr">
@@ -32428,7 +32428,7 @@
       <c r="A82" s="0"/>
       <c r="B82" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲?</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="C82" s="24" t="inlineStr">
@@ -32510,7 +32510,7 @@
       <c r="I83" s="22"/>
       <c r="J83" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞?</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="K83" s="24" t="inlineStr">
@@ -32758,7 +32758,7 @@
       <c r="S88" s="22"/>
       <c r="T88" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢?</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="U88" s="24" t="inlineStr">
@@ -32856,7 +32856,7 @@
       </c>
       <c r="J90" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋?</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="K90" s="24" t="inlineStr">
@@ -32907,7 +32907,7 @@
       <c r="E91" s="22"/>
       <c r="F91" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞?</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="G91" s="24" t="inlineStr">
@@ -33036,7 +33036,7 @@
       <c r="G93" s="22"/>
       <c r="H93" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">林?</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="I93" s="24" t="inlineStr">
@@ -33256,7 +33256,7 @@
       <c r="E97" s="22"/>
       <c r="F97" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞?</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="G97" s="24" t="inlineStr">
@@ -33420,7 +33420,7 @@
       <c r="G101" s="22"/>
       <c r="H101" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">無?</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="I101" s="24" t="inlineStr">
@@ -33575,7 +33575,7 @@
       <c r="E104" s="22"/>
       <c r="F104" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲?</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="G104" s="24" t="inlineStr">
@@ -33646,7 +33646,7 @@
       <c r="Q105" s="22"/>
       <c r="R105" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲?</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="S105" s="24" t="inlineStr">
@@ -33712,7 +33712,7 @@
       <c r="M107" s="22"/>
       <c r="N107" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">無?</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="O107" s="24" t="inlineStr">
@@ -33826,7 +33826,7 @@
       <c r="M110" s="22"/>
       <c r="N110" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲?</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="O110" s="24" t="inlineStr">
@@ -33999,7 +33999,7 @@
       <c r="I115" s="22"/>
       <c r="J115" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">㒇?</t>
+          <t xml:space="preserve">㒇</t>
         </is>
       </c>
       <c r="K115" s="24" t="inlineStr">
@@ -34371,7 +34371,7 @@
       <c r="L122" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-仲?</t>
+仲</t>
         </is>
       </c>
       <c r="M122" s="24" t="inlineStr">
@@ -34382,7 +34382,7 @@
       <c r="N122" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–)
-仲?</t>
+仲</t>
         </is>
       </c>
       <c r="O122" s="24" t="inlineStr">
@@ -34486,7 +34486,7 @@
       <c r="N124" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–)
-仲?</t>
+仲</t>
         </is>
       </c>
       <c r="O124" s="24" t="inlineStr">
@@ -34660,7 +34660,7 @@
       <c r="I129" s="22"/>
       <c r="J129" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">林?</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="K129" s="24" t="inlineStr">
@@ -34806,7 +34806,7 @@
       <c r="I132" s="22"/>
       <c r="J132" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰?</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="K132" s="24" t="inlineStr">

--- a/sheets/대금율보/검수/대금산조 중중모리.xlsx
+++ b/sheets/대금율보/검수/대금산조 중중모리.xlsx
@@ -28389,32 +28389,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="13.46" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13.46" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="13.46" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="13.46" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="13.46" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="13.46" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="13.46" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="13.46" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="13.46" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="13.46" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="93.02" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -28441,7 +28441,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="138.71" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -28504,7 +28504,7 @@
       </c>
       <c r="U3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="138.71" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -28543,7 +28543,7 @@
       <c r="T4" s="21"/>
       <c r="U4" s="22"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="138.71" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -28592,7 +28592,7 @@
       <c r="T5" s="21"/>
       <c r="U5" s="22"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="138.71" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -28648,7 +28648,7 @@
       </c>
       <c r="U6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="138.71" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -28700,7 +28700,7 @@
       </c>
       <c r="U7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="138.71" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="22"/>
@@ -28745,7 +28745,7 @@
       <c r="T8" s="21"/>
       <c r="U8" s="22"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="138.71" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -28809,7 +28809,7 @@
       </c>
       <c r="U9" s="22"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="138.71" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
       <c r="T10" s="21"/>
       <c r="U10" s="22"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="138.71" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
@@ -28897,7 +28897,7 @@
       <c r="T11" s="21"/>
       <c r="U11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="138.71" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -28958,7 +28958,7 @@
       </c>
       <c r="U12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="138.71" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="22"/>
@@ -29006,7 +29006,7 @@
       </c>
       <c r="U13" s="22"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="138.71" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -29068,10 +29068,10 @@
       <c r="T14" s="21"/>
       <c r="U14" s="22"/>
     </row>
-    <row r="15">
+    <row r="15" ht="6.0" customHeight="true">
       <c r="A15" s="0"/>
     </row>
-    <row r="16" ht="60" customHeight="1">
+    <row r="16" ht="93.02" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="20" t="inlineStr">
         <is>
@@ -29098,7 +29098,7 @@
       <c r="T16" s="20"/>
       <c r="U16" s="20"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="138.71" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -29159,7 +29159,7 @@
       </c>
       <c r="U17" s="22"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="138.71" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -29207,7 +29207,7 @@
       </c>
       <c r="U18" s="22"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="138.71" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
@@ -29259,7 +29259,7 @@
       <c r="T19" s="21"/>
       <c r="U19" s="22"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="138.71" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21" t="inlineStr">
         <is>
@@ -29308,7 +29308,7 @@
       </c>
       <c r="U20" s="22"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="138.71" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21" t="inlineStr">
         <is>
@@ -29365,7 +29365,7 @@
       </c>
       <c r="U21" s="22"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="138.71" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="22" t="inlineStr">
@@ -29413,7 +29413,7 @@
       </c>
       <c r="U22" s="22"/>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="138.71" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
       </c>
       <c r="U23" s="22"/>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="138.71" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21" t="inlineStr">
         <is>
@@ -29509,7 +29509,7 @@
       </c>
       <c r="U24" s="22"/>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="138.71" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21" t="inlineStr">
         <is>
@@ -29555,7 +29555,7 @@
       </c>
       <c r="U25" s="22"/>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="138.71" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="22"/>
@@ -29603,7 +29603,7 @@
       </c>
       <c r="U26" s="22"/>
     </row>
-    <row r="27" ht="56" customHeight="1">
+    <row r="27" ht="138.71" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="23" t="inlineStr">
         <is>
@@ -29654,7 +29654,7 @@
       </c>
       <c r="U27" s="22"/>
     </row>
-    <row r="28" ht="56" customHeight="1">
+    <row r="28" ht="138.71" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21" t="inlineStr">
         <is>
@@ -29709,10 +29709,10 @@
       </c>
       <c r="U28" s="22"/>
     </row>
-    <row r="29">
+    <row r="29" ht="6.0" customHeight="true">
       <c r="A29" s="0"/>
     </row>
-    <row r="30" ht="60" customHeight="1">
+    <row r="30" ht="93.02" customHeight="true">
       <c r="A30" s="0"/>
       <c r="B30" s="20" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
       <c r="T30" s="20"/>
       <c r="U30" s="20"/>
     </row>
-    <row r="31" ht="56" customHeight="1">
+    <row r="31" ht="138.71" customHeight="true">
       <c r="A31" s="0"/>
       <c r="B31" s="21" t="inlineStr">
         <is>
@@ -29804,7 +29804,7 @@
       </c>
       <c r="U31" s="22"/>
     </row>
-    <row r="32" ht="56" customHeight="1">
+    <row r="32" ht="138.71" customHeight="true">
       <c r="A32" s="0"/>
       <c r="B32" s="21" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
       </c>
       <c r="U32" s="22"/>
     </row>
-    <row r="33" ht="56" customHeight="1">
+    <row r="33" ht="138.71" customHeight="true">
       <c r="A33" s="0"/>
       <c r="B33" s="21" t="inlineStr">
         <is>
@@ -29940,7 +29940,7 @@
       </c>
       <c r="U33" s="22"/>
     </row>
-    <row r="34" ht="56" customHeight="1">
+    <row r="34" ht="138.71" customHeight="true">
       <c r="A34" s="0"/>
       <c r="B34" s="21" t="inlineStr">
         <is>
@@ -29995,7 +29995,7 @@
       </c>
       <c r="U34" s="22"/>
     </row>
-    <row r="35" ht="56" customHeight="1">
+    <row r="35" ht="138.71" customHeight="true">
       <c r="A35" s="0"/>
       <c r="B35" s="23" t="inlineStr">
         <is>
@@ -30051,7 +30051,7 @@
       <c r="T35" s="21"/>
       <c r="U35" s="22"/>
     </row>
-    <row r="36" ht="56" customHeight="1">
+    <row r="36" ht="138.71" customHeight="true">
       <c r="A36" s="0"/>
       <c r="B36" s="21" t="inlineStr">
         <is>
@@ -30113,7 +30113,7 @@
       </c>
       <c r="U36" s="22"/>
     </row>
-    <row r="37" ht="56" customHeight="1">
+    <row r="37" ht="138.71" customHeight="true">
       <c r="A37" s="0"/>
       <c r="B37" s="21" t="inlineStr">
         <is>
@@ -30172,7 +30172,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="56" customHeight="1">
+    <row r="38" ht="138.71" customHeight="true">
       <c r="A38" s="0"/>
       <c r="B38" s="21" t="inlineStr">
         <is>
@@ -30222,7 +30222,7 @@
       </c>
       <c r="U38" s="22"/>
     </row>
-    <row r="39" ht="56" customHeight="1">
+    <row r="39" ht="138.71" customHeight="true">
       <c r="A39" s="0"/>
       <c r="B39" s="21" t="inlineStr">
         <is>
@@ -30273,7 +30273,7 @@
       </c>
       <c r="U39" s="22"/>
     </row>
-    <row r="40" ht="56" customHeight="1">
+    <row r="40" ht="138.71" customHeight="true">
       <c r="A40" s="0"/>
       <c r="B40" s="21"/>
       <c r="C40" s="22"/>
@@ -30321,7 +30321,7 @@
       </c>
       <c r="U40" s="22"/>
     </row>
-    <row r="41" ht="56" customHeight="1">
+    <row r="41" ht="138.71" customHeight="true">
       <c r="A41" s="0"/>
       <c r="B41" s="21" t="inlineStr">
         <is>
@@ -30368,7 +30368,7 @@
       </c>
       <c r="U41" s="22"/>
     </row>
-    <row r="42" ht="56" customHeight="1">
+    <row r="42" ht="138.71" customHeight="true">
       <c r="A42" s="0"/>
       <c r="B42" s="21" t="inlineStr">
         <is>
@@ -30437,10 +30437,10 @@
       </c>
       <c r="U42" s="22"/>
     </row>
-    <row r="43">
+    <row r="43" ht="6.0" customHeight="true">
       <c r="A43" s="0"/>
     </row>
-    <row r="44" ht="60" customHeight="1">
+    <row r="44" ht="93.02" customHeight="true">
       <c r="A44" s="0"/>
       <c r="B44" s="20" t="inlineStr">
         <is>
@@ -30467,7 +30467,7 @@
       <c r="T44" s="20"/>
       <c r="U44" s="20"/>
     </row>
-    <row r="45" ht="56" customHeight="1">
+    <row r="45" ht="138.71" customHeight="true">
       <c r="A45" s="0"/>
       <c r="B45" s="21" t="inlineStr">
         <is>
@@ -30537,7 +30537,7 @@
       </c>
       <c r="U45" s="22"/>
     </row>
-    <row r="46" ht="56" customHeight="1">
+    <row r="46" ht="138.71" customHeight="true">
       <c r="A46" s="0"/>
       <c r="B46" s="21"/>
       <c r="C46" s="22"/>
@@ -30598,7 +30598,7 @@
       </c>
       <c r="U46" s="22"/>
     </row>
-    <row r="47" ht="56" customHeight="1">
+    <row r="47" ht="138.71" customHeight="true">
       <c r="A47" s="0"/>
       <c r="B47" s="21"/>
       <c r="C47" s="22"/>
@@ -30647,7 +30647,7 @@
       </c>
       <c r="U47" s="22"/>
     </row>
-    <row r="48" ht="56" customHeight="1">
+    <row r="48" ht="138.71" customHeight="true">
       <c r="A48" s="0"/>
       <c r="B48" s="21" t="inlineStr">
         <is>
@@ -30708,7 +30708,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="56" customHeight="1">
+    <row r="49" ht="138.71" customHeight="true">
       <c r="A49" s="0"/>
       <c r="B49" s="21" t="inlineStr">
         <is>
@@ -30771,7 +30771,7 @@
       </c>
       <c r="U49" s="22"/>
     </row>
-    <row r="50" ht="56" customHeight="1">
+    <row r="50" ht="138.71" customHeight="true">
       <c r="A50" s="0"/>
       <c r="B50" s="21" t="inlineStr">
         <is>
@@ -30815,7 +30815,7 @@
       <c r="T50" s="21"/>
       <c r="U50" s="22"/>
     </row>
-    <row r="51" ht="56" customHeight="1">
+    <row r="51" ht="138.71" customHeight="true">
       <c r="A51" s="0"/>
       <c r="B51" s="21"/>
       <c r="C51" s="22" t="inlineStr">
@@ -30873,7 +30873,7 @@
       </c>
       <c r="U51" s="22"/>
     </row>
-    <row r="52" ht="56" customHeight="1">
+    <row r="52" ht="138.71" customHeight="true">
       <c r="A52" s="0"/>
       <c r="B52" s="21" t="inlineStr">
         <is>
@@ -30926,7 +30926,7 @@
       </c>
       <c r="U52" s="22"/>
     </row>
-    <row r="53" ht="56" customHeight="1">
+    <row r="53" ht="138.71" customHeight="true">
       <c r="A53" s="0"/>
       <c r="B53" s="21" t="inlineStr">
         <is>
@@ -30980,7 +30980,7 @@
       </c>
       <c r="U53" s="22"/>
     </row>
-    <row r="54" ht="56" customHeight="1">
+    <row r="54" ht="138.71" customHeight="true">
       <c r="A54" s="0"/>
       <c r="B54" s="21" t="inlineStr">
         <is>
@@ -31031,7 +31031,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="56" customHeight="1">
+    <row r="55" ht="138.71" customHeight="true">
       <c r="A55" s="0"/>
       <c r="B55" s="21"/>
       <c r="C55" s="22"/>
@@ -31067,7 +31067,7 @@
       </c>
       <c r="U55" s="22"/>
     </row>
-    <row r="56" ht="56" customHeight="1">
+    <row r="56" ht="138.71" customHeight="true">
       <c r="A56" s="0"/>
       <c r="B56" s="21" t="inlineStr">
         <is>
@@ -31119,10 +31119,10 @@
       <c r="T56" s="21"/>
       <c r="U56" s="22"/>
     </row>
-    <row r="57">
+    <row r="57" ht="6.0" customHeight="true">
       <c r="A57" s="0"/>
     </row>
-    <row r="58" ht="60" customHeight="1">
+    <row r="58" ht="93.02" customHeight="true">
       <c r="A58" s="0"/>
       <c r="B58" s="20" t="inlineStr">
         <is>
@@ -31149,7 +31149,7 @@
       <c r="T58" s="20"/>
       <c r="U58" s="20"/>
     </row>
-    <row r="59" ht="56" customHeight="1">
+    <row r="59" ht="138.71" customHeight="true">
       <c r="A59" s="0"/>
       <c r="B59" s="21" t="inlineStr">
         <is>
@@ -31220,7 +31220,7 @@
       </c>
       <c r="U59" s="22"/>
     </row>
-    <row r="60" ht="56" customHeight="1">
+    <row r="60" ht="138.71" customHeight="true">
       <c r="A60" s="0"/>
       <c r="B60" s="21" t="inlineStr">
         <is>
@@ -31286,7 +31286,7 @@
       </c>
       <c r="U60" s="22"/>
     </row>
-    <row r="61" ht="56" customHeight="1">
+    <row r="61" ht="138.71" customHeight="true">
       <c r="A61" s="0"/>
       <c r="B61" s="21" t="inlineStr">
         <is>
@@ -31348,7 +31348,7 @@
       </c>
       <c r="U61" s="22"/>
     </row>
-    <row r="62" ht="56" customHeight="1">
+    <row r="62" ht="138.71" customHeight="true">
       <c r="A62" s="0"/>
       <c r="B62" s="21" t="inlineStr">
         <is>
@@ -31409,7 +31409,7 @@
       </c>
       <c r="U62" s="22"/>
     </row>
-    <row r="63" ht="56" customHeight="1">
+    <row r="63" ht="138.71" customHeight="true">
       <c r="A63" s="0"/>
       <c r="B63" s="21" t="inlineStr">
         <is>
@@ -31467,7 +31467,7 @@
       </c>
       <c r="U63" s="22"/>
     </row>
-    <row r="64" ht="56" customHeight="1">
+    <row r="64" ht="138.71" customHeight="true">
       <c r="A64" s="0"/>
       <c r="B64" s="21" t="inlineStr">
         <is>
@@ -31510,7 +31510,7 @@
       </c>
       <c r="U64" s="22"/>
     </row>
-    <row r="65" ht="56" customHeight="1">
+    <row r="65" ht="138.71" customHeight="true">
       <c r="A65" s="0"/>
       <c r="B65" s="21" t="inlineStr">
         <is>
@@ -31567,7 +31567,7 @@
       </c>
       <c r="U65" s="22"/>
     </row>
-    <row r="66" ht="56" customHeight="1">
+    <row r="66" ht="138.71" customHeight="true">
       <c r="A66" s="0"/>
       <c r="B66" s="21" t="inlineStr">
         <is>
@@ -31626,7 +31626,7 @@
       </c>
       <c r="U66" s="22"/>
     </row>
-    <row r="67" ht="56" customHeight="1">
+    <row r="67" ht="138.71" customHeight="true">
       <c r="A67" s="0"/>
       <c r="B67" s="21" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
       </c>
       <c r="U67" s="22"/>
     </row>
-    <row r="68" ht="56" customHeight="1">
+    <row r="68" ht="138.71" customHeight="true">
       <c r="A68" s="0"/>
       <c r="B68" s="21" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
       </c>
       <c r="U68" s="22"/>
     </row>
-    <row r="69" ht="56" customHeight="1">
+    <row r="69" ht="138.71" customHeight="true">
       <c r="A69" s="0"/>
       <c r="B69" s="21" t="inlineStr">
         <is>
@@ -31799,7 +31799,7 @@
       </c>
       <c r="U69" s="22"/>
     </row>
-    <row r="70" ht="56" customHeight="1">
+    <row r="70" ht="138.71" customHeight="true">
       <c r="A70" s="0"/>
       <c r="B70" s="21" t="inlineStr">
         <is>
@@ -31856,10 +31856,10 @@
       </c>
       <c r="U70" s="22"/>
     </row>
-    <row r="71">
+    <row r="71" ht="6.0" customHeight="true">
       <c r="A71" s="0"/>
     </row>
-    <row r="72" ht="60" customHeight="1">
+    <row r="72" ht="93.02" customHeight="true">
       <c r="A72" s="0"/>
       <c r="B72" s="20" t="inlineStr">
         <is>
@@ -31886,7 +31886,7 @@
       <c r="T72" s="20"/>
       <c r="U72" s="20"/>
     </row>
-    <row r="73" ht="56" customHeight="1">
+    <row r="73" ht="138.71" customHeight="true">
       <c r="A73" s="0"/>
       <c r="B73" s="21" t="inlineStr">
         <is>
@@ -31959,7 +31959,7 @@
       </c>
       <c r="U73" s="22"/>
     </row>
-    <row r="74" ht="56" customHeight="1">
+    <row r="74" ht="138.71" customHeight="true">
       <c r="A74" s="0"/>
       <c r="B74" s="21" t="inlineStr">
         <is>
@@ -32013,7 +32013,7 @@
       </c>
       <c r="U74" s="22"/>
     </row>
-    <row r="75" ht="56" customHeight="1">
+    <row r="75" ht="138.71" customHeight="true">
       <c r="A75" s="0"/>
       <c r="B75" s="21" t="inlineStr">
         <is>
@@ -32070,7 +32070,7 @@
       </c>
       <c r="U75" s="22"/>
     </row>
-    <row r="76" ht="56" customHeight="1">
+    <row r="76" ht="138.71" customHeight="true">
       <c r="A76" s="0"/>
       <c r="B76" s="21" t="inlineStr">
         <is>
@@ -32134,7 +32134,7 @@
       </c>
       <c r="U76" s="22"/>
     </row>
-    <row r="77" ht="56" customHeight="1">
+    <row r="77" ht="138.71" customHeight="true">
       <c r="A77" s="0"/>
       <c r="B77" s="21" t="inlineStr">
         <is>
@@ -32198,7 +32198,7 @@
       </c>
       <c r="U77" s="22"/>
     </row>
-    <row r="78" ht="56" customHeight="1">
+    <row r="78" ht="138.71" customHeight="true">
       <c r="A78" s="0"/>
       <c r="B78" s="21" t="inlineStr">
         <is>
@@ -32253,7 +32253,7 @@
       </c>
       <c r="U78" s="22"/>
     </row>
-    <row r="79" ht="56" customHeight="1">
+    <row r="79" ht="138.71" customHeight="true">
       <c r="A79" s="0"/>
       <c r="B79" s="21" t="inlineStr">
         <is>
@@ -32317,7 +32317,7 @@
       </c>
       <c r="U79" s="22"/>
     </row>
-    <row r="80" ht="56" customHeight="1">
+    <row r="80" ht="138.71" customHeight="true">
       <c r="A80" s="0"/>
       <c r="B80" s="21" t="inlineStr">
         <is>
@@ -32370,7 +32370,7 @@
       </c>
       <c r="U80" s="22"/>
     </row>
-    <row r="81" ht="56" customHeight="1">
+    <row r="81" ht="138.71" customHeight="true">
       <c r="A81" s="0"/>
       <c r="B81" s="21" t="inlineStr">
         <is>
@@ -32424,7 +32424,7 @@
       </c>
       <c r="U81" s="22"/>
     </row>
-    <row r="82" ht="56" customHeight="1">
+    <row r="82" ht="138.71" customHeight="true">
       <c r="A82" s="0"/>
       <c r="B82" s="23" t="inlineStr">
         <is>
@@ -32489,7 +32489,7 @@
       </c>
       <c r="U82" s="22"/>
     </row>
-    <row r="83" ht="56" customHeight="1">
+    <row r="83" ht="138.71" customHeight="true">
       <c r="A83" s="0"/>
       <c r="B83" s="21" t="inlineStr">
         <is>
@@ -32541,7 +32541,7 @@
       </c>
       <c r="U83" s="22"/>
     </row>
-    <row r="84" ht="56" customHeight="1">
+    <row r="84" ht="138.71" customHeight="true">
       <c r="A84" s="0"/>
       <c r="B84" s="21" t="inlineStr">
         <is>
@@ -32605,10 +32605,10 @@
       </c>
       <c r="U84" s="22"/>
     </row>
-    <row r="85">
+    <row r="85" ht="6.0" customHeight="true">
       <c r="A85" s="0"/>
     </row>
-    <row r="86" ht="60" customHeight="1">
+    <row r="86" ht="93.02" customHeight="true">
       <c r="A86" s="0"/>
       <c r="B86" s="20" t="inlineStr">
         <is>
@@ -32635,7 +32635,7 @@
       <c r="T86" s="20"/>
       <c r="U86" s="20"/>
     </row>
-    <row r="87" ht="56" customHeight="1">
+    <row r="87" ht="138.71" customHeight="true">
       <c r="A87" s="0"/>
       <c r="B87" s="21" t="inlineStr">
         <is>
@@ -32703,7 +32703,7 @@
       </c>
       <c r="U87" s="22"/>
     </row>
-    <row r="88" ht="56" customHeight="1">
+    <row r="88" ht="138.71" customHeight="true">
       <c r="A88" s="0"/>
       <c r="B88" s="21" t="inlineStr">
         <is>
@@ -32767,7 +32767,7 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="56" customHeight="1">
+    <row r="89" ht="138.71" customHeight="true">
       <c r="A89" s="0"/>
       <c r="B89" s="21" t="inlineStr">
         <is>
@@ -32827,7 +32827,7 @@
       </c>
       <c r="U89" s="22"/>
     </row>
-    <row r="90" ht="56" customHeight="1">
+    <row r="90" ht="138.71" customHeight="true">
       <c r="A90" s="0"/>
       <c r="B90" s="21" t="inlineStr">
         <is>
@@ -32890,7 +32890,7 @@
       </c>
       <c r="U90" s="22"/>
     </row>
-    <row r="91" ht="56" customHeight="1">
+    <row r="91" ht="138.71" customHeight="true">
       <c r="A91" s="0"/>
       <c r="B91" s="21" t="inlineStr">
         <is>
@@ -32955,7 +32955,7 @@
       </c>
       <c r="U91" s="22"/>
     </row>
-    <row r="92" ht="56" customHeight="1">
+    <row r="92" ht="138.71" customHeight="true">
       <c r="A92" s="0"/>
       <c r="B92" s="21" t="inlineStr">
         <is>
@@ -33013,7 +33013,7 @@
       </c>
       <c r="U92" s="22"/>
     </row>
-    <row r="93" ht="56" customHeight="1">
+    <row r="93" ht="138.71" customHeight="true">
       <c r="A93" s="0"/>
       <c r="B93" s="21" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
       </c>
       <c r="U93" s="22"/>
     </row>
-    <row r="94" ht="56" customHeight="1">
+    <row r="94" ht="138.71" customHeight="true">
       <c r="A94" s="0"/>
       <c r="B94" s="21" t="inlineStr">
         <is>
@@ -33132,7 +33132,7 @@
       </c>
       <c r="U94" s="22"/>
     </row>
-    <row r="95" ht="56" customHeight="1">
+    <row r="95" ht="138.71" customHeight="true">
       <c r="A95" s="0"/>
       <c r="B95" s="21" t="inlineStr">
         <is>
@@ -33190,7 +33190,7 @@
       </c>
       <c r="U95" s="22"/>
     </row>
-    <row r="96" ht="56" customHeight="1">
+    <row r="96" ht="138.71" customHeight="true">
       <c r="A96" s="0"/>
       <c r="B96" s="21"/>
       <c r="C96" s="22"/>
@@ -33240,7 +33240,7 @@
       <c r="T96" s="21"/>
       <c r="U96" s="22"/>
     </row>
-    <row r="97" ht="56" customHeight="1">
+    <row r="97" ht="138.71" customHeight="true">
       <c r="A97" s="0"/>
       <c r="B97" s="21" t="inlineStr">
         <is>
@@ -33300,7 +33300,7 @@
       </c>
       <c r="U97" s="22"/>
     </row>
-    <row r="98" ht="56" customHeight="1">
+    <row r="98" ht="138.71" customHeight="true">
       <c r="A98" s="0"/>
       <c r="B98" s="21" t="inlineStr">
         <is>
@@ -33368,10 +33368,10 @@
       </c>
       <c r="U98" s="22"/>
     </row>
-    <row r="99">
+    <row r="99" ht="6.0" customHeight="true">
       <c r="A99" s="0"/>
     </row>
-    <row r="100" ht="60" customHeight="1">
+    <row r="100" ht="93.02" customHeight="true">
       <c r="A100" s="0"/>
       <c r="B100" s="20" t="inlineStr">
         <is>
@@ -33398,7 +33398,7 @@
       <c r="T100" s="20"/>
       <c r="U100" s="20"/>
     </row>
-    <row r="101" ht="56" customHeight="1">
+    <row r="101" ht="138.71" customHeight="true">
       <c r="A101" s="0"/>
       <c r="B101" s="21" t="inlineStr">
         <is>
@@ -33466,7 +33466,7 @@
       </c>
       <c r="U101" s="22"/>
     </row>
-    <row r="102" ht="56" customHeight="1">
+    <row r="102" ht="138.71" customHeight="true">
       <c r="A102" s="0"/>
       <c r="B102" s="21" t="inlineStr">
         <is>
@@ -33524,7 +33524,7 @@
       <c r="T102" s="21"/>
       <c r="U102" s="22"/>
     </row>
-    <row r="103" ht="56" customHeight="1">
+    <row r="103" ht="138.71" customHeight="true">
       <c r="A103" s="0"/>
       <c r="B103" s="21"/>
       <c r="C103" s="22"/>
@@ -33567,7 +33567,7 @@
       <c r="T103" s="21"/>
       <c r="U103" s="22"/>
     </row>
-    <row r="104" ht="56" customHeight="1">
+    <row r="104" ht="138.71" customHeight="true">
       <c r="A104" s="0"/>
       <c r="B104" s="21"/>
       <c r="C104" s="22"/>
@@ -33614,7 +33614,7 @@
       <c r="T104" s="21"/>
       <c r="U104" s="22"/>
     </row>
-    <row r="105" ht="56" customHeight="1">
+    <row r="105" ht="138.71" customHeight="true">
       <c r="A105" s="0"/>
       <c r="B105" s="21"/>
       <c r="C105" s="22"/>
@@ -33657,7 +33657,7 @@
       <c r="T105" s="21"/>
       <c r="U105" s="22"/>
     </row>
-    <row r="106" ht="56" customHeight="1">
+    <row r="106" ht="138.71" customHeight="true">
       <c r="A106" s="0"/>
       <c r="B106" s="21"/>
       <c r="C106" s="22"/>
@@ -33688,7 +33688,7 @@
       <c r="T106" s="21"/>
       <c r="U106" s="22"/>
     </row>
-    <row r="107" ht="56" customHeight="1">
+    <row r="107" ht="138.71" customHeight="true">
       <c r="A107" s="0"/>
       <c r="B107" s="21"/>
       <c r="C107" s="22"/>
@@ -33731,7 +33731,7 @@
       <c r="T107" s="21"/>
       <c r="U107" s="22"/>
     </row>
-    <row r="108" ht="56" customHeight="1">
+    <row r="108" ht="138.71" customHeight="true">
       <c r="A108" s="0"/>
       <c r="B108" s="21"/>
       <c r="C108" s="22"/>
@@ -33767,7 +33767,7 @@
       <c r="T108" s="21"/>
       <c r="U108" s="22"/>
     </row>
-    <row r="109" ht="56" customHeight="1">
+    <row r="109" ht="138.71" customHeight="true">
       <c r="A109" s="0"/>
       <c r="B109" s="21"/>
       <c r="C109" s="22"/>
@@ -33802,7 +33802,7 @@
       <c r="T109" s="21"/>
       <c r="U109" s="22"/>
     </row>
-    <row r="110" ht="56" customHeight="1">
+    <row r="110" ht="138.71" customHeight="true">
       <c r="A110" s="0"/>
       <c r="B110" s="21"/>
       <c r="C110" s="22"/>
@@ -33841,7 +33841,7 @@
       <c r="T110" s="21"/>
       <c r="U110" s="22"/>
     </row>
-    <row r="111" ht="56" customHeight="1">
+    <row r="111" ht="138.71" customHeight="true">
       <c r="A111" s="0"/>
       <c r="B111" s="21"/>
       <c r="C111" s="22"/>
@@ -33876,7 +33876,7 @@
       <c r="T111" s="21"/>
       <c r="U111" s="22"/>
     </row>
-    <row r="112" ht="56" customHeight="1">
+    <row r="112" ht="138.71" customHeight="true">
       <c r="A112" s="0"/>
       <c r="B112" s="21" t="inlineStr">
         <is>
@@ -33941,10 +33941,10 @@
       </c>
       <c r="U112" s="22"/>
     </row>
-    <row r="113">
+    <row r="113" ht="6.0" customHeight="true">
       <c r="A113" s="0"/>
     </row>
-    <row r="114" ht="60" customHeight="1">
+    <row r="114" ht="93.02" customHeight="true">
       <c r="A114" s="0"/>
       <c r="B114" s="20" t="inlineStr">
         <is>
@@ -33971,7 +33971,7 @@
       <c r="T114" s="20"/>
       <c r="U114" s="20"/>
     </row>
-    <row r="115" ht="56" customHeight="1">
+    <row r="115" ht="138.71" customHeight="true">
       <c r="A115" s="0"/>
       <c r="B115" s="21" t="inlineStr">
         <is>
@@ -34041,7 +34041,7 @@
       </c>
       <c r="U115" s="22"/>
     </row>
-    <row r="116" ht="56" customHeight="1">
+    <row r="116" ht="138.71" customHeight="true">
       <c r="A116" s="0"/>
       <c r="B116" s="21"/>
       <c r="C116" s="22"/>
@@ -34095,7 +34095,7 @@
       </c>
       <c r="U116" s="22"/>
     </row>
-    <row r="117" ht="56" customHeight="1">
+    <row r="117" ht="138.71" customHeight="true">
       <c r="A117" s="0"/>
       <c r="B117" s="21" t="inlineStr">
         <is>
@@ -34142,7 +34142,7 @@
       </c>
       <c r="U117" s="22"/>
     </row>
-    <row r="118" ht="56" customHeight="1">
+    <row r="118" ht="138.71" customHeight="true">
       <c r="A118" s="0"/>
       <c r="B118" s="21"/>
       <c r="C118" s="22"/>
@@ -34194,7 +34194,7 @@
       </c>
       <c r="U118" s="22"/>
     </row>
-    <row r="119" ht="56" customHeight="1">
+    <row r="119" ht="138.71" customHeight="true">
       <c r="A119" s="0"/>
       <c r="B119" s="21" t="inlineStr">
         <is>
@@ -34238,7 +34238,7 @@
       </c>
       <c r="U119" s="22"/>
     </row>
-    <row r="120" ht="56" customHeight="1">
+    <row r="120" ht="138.71" customHeight="true">
       <c r="A120" s="0"/>
       <c r="B120" s="21" t="inlineStr">
         <is>
@@ -34282,7 +34282,7 @@
       </c>
       <c r="U120" s="22"/>
     </row>
-    <row r="121" ht="56" customHeight="1">
+    <row r="121" ht="138.71" customHeight="true">
       <c r="A121" s="0"/>
       <c r="B121" s="21" t="inlineStr">
         <is>
@@ -34344,7 +34344,7 @@
       </c>
       <c r="U121" s="26"/>
     </row>
-    <row r="122" ht="56" customHeight="1">
+    <row r="122" ht="138.71" customHeight="true">
       <c r="A122" s="0"/>
       <c r="B122" s="21"/>
       <c r="C122" s="22"/>
@@ -34405,7 +34405,7 @@
       <c r="T122" s="21"/>
       <c r="U122" s="22"/>
     </row>
-    <row r="123" ht="56" customHeight="1">
+    <row r="123" ht="138.71" customHeight="true">
       <c r="A123" s="0"/>
       <c r="B123" s="21" t="inlineStr">
         <is>
@@ -34453,7 +34453,7 @@
       <c r="T123" s="21"/>
       <c r="U123" s="22"/>
     </row>
-    <row r="124" ht="56" customHeight="1">
+    <row r="124" ht="138.71" customHeight="true">
       <c r="A124" s="0"/>
       <c r="B124" s="21"/>
       <c r="C124" s="22"/>
@@ -34511,7 +34511,7 @@
       <c r="T124" s="21"/>
       <c r="U124" s="22"/>
     </row>
-    <row r="125" ht="56" customHeight="1">
+    <row r="125" ht="138.71" customHeight="true">
       <c r="A125" s="0"/>
       <c r="B125" s="21" t="inlineStr">
         <is>
@@ -34558,7 +34558,7 @@
       <c r="T125" s="21"/>
       <c r="U125" s="22"/>
     </row>
-    <row r="126" ht="56" customHeight="1">
+    <row r="126" ht="138.71" customHeight="true">
       <c r="A126" s="0"/>
       <c r="B126" s="21"/>
       <c r="C126" s="22"/>
@@ -34618,10 +34618,10 @@
       </c>
       <c r="U126" s="22"/>
     </row>
-    <row r="127">
+    <row r="127" ht="6.0" customHeight="true">
       <c r="A127" s="0"/>
     </row>
-    <row r="128" ht="60" customHeight="1">
+    <row r="128" ht="93.02" customHeight="true">
       <c r="A128" s="0"/>
       <c r="B128" s="20" t="inlineStr">
         <is>
@@ -34648,7 +34648,7 @@
       <c r="T128" s="20"/>
       <c r="U128" s="20"/>
     </row>
-    <row r="129" ht="56" customHeight="1">
+    <row r="129" ht="138.71" customHeight="true">
       <c r="A129" s="0"/>
       <c r="B129" s="21"/>
       <c r="C129" s="22"/>
@@ -34699,7 +34699,7 @@
       </c>
       <c r="U129" s="22"/>
     </row>
-    <row r="130" ht="56" customHeight="1">
+    <row r="130" ht="138.71" customHeight="true">
       <c r="A130" s="0"/>
       <c r="B130" s="21"/>
       <c r="C130" s="22"/>
@@ -34749,7 +34749,7 @@
       </c>
       <c r="U130" s="22"/>
     </row>
-    <row r="131" ht="56" customHeight="1">
+    <row r="131" ht="138.71" customHeight="true">
       <c r="A131" s="0"/>
       <c r="B131" s="21"/>
       <c r="C131" s="22"/>
@@ -34794,7 +34794,7 @@
       </c>
       <c r="U131" s="22"/>
     </row>
-    <row r="132" ht="56" customHeight="1">
+    <row r="132" ht="138.71" customHeight="true">
       <c r="A132" s="0"/>
       <c r="B132" s="21"/>
       <c r="C132" s="22"/>
@@ -34833,7 +34833,7 @@
       <c r="T132" s="21"/>
       <c r="U132" s="22"/>
     </row>
-    <row r="133" ht="56" customHeight="1">
+    <row r="133" ht="138.71" customHeight="true">
       <c r="A133" s="0"/>
       <c r="B133" s="21"/>
       <c r="C133" s="22"/>
@@ -34872,7 +34872,7 @@
       </c>
       <c r="U133" s="22"/>
     </row>
-    <row r="134" ht="56" customHeight="1">
+    <row r="134" ht="138.71" customHeight="true">
       <c r="A134" s="0"/>
       <c r="B134" s="21"/>
       <c r="C134" s="22"/>
@@ -34911,7 +34911,7 @@
       <c r="T134" s="21"/>
       <c r="U134" s="22"/>
     </row>
-    <row r="135" ht="56" customHeight="1">
+    <row r="135" ht="138.71" customHeight="true">
       <c r="A135" s="0"/>
       <c r="B135" s="21"/>
       <c r="C135" s="22"/>
@@ -34955,7 +34955,7 @@
       </c>
       <c r="U135" s="22"/>
     </row>
-    <row r="136" ht="56" customHeight="1">
+    <row r="136" ht="138.71" customHeight="true">
       <c r="A136" s="0"/>
       <c r="B136" s="21"/>
       <c r="C136" s="22"/>
@@ -34997,7 +34997,7 @@
       </c>
       <c r="U136" s="22"/>
     </row>
-    <row r="137" ht="56" customHeight="1">
+    <row r="137" ht="138.71" customHeight="true">
       <c r="A137" s="0"/>
       <c r="B137" s="21"/>
       <c r="C137" s="22"/>
@@ -35032,7 +35032,7 @@
       </c>
       <c r="U137" s="22"/>
     </row>
-    <row r="138" ht="56" customHeight="1">
+    <row r="138" ht="138.71" customHeight="true">
       <c r="A138" s="0"/>
       <c r="B138" s="21"/>
       <c r="C138" s="22"/>
@@ -35072,7 +35072,7 @@
       <c r="T138" s="21"/>
       <c r="U138" s="22"/>
     </row>
-    <row r="139" ht="56" customHeight="1">
+    <row r="139" ht="138.71" customHeight="true">
       <c r="A139" s="0"/>
       <c r="B139" s="21"/>
       <c r="C139" s="22"/>
@@ -35115,7 +35115,7 @@
       </c>
       <c r="U139" s="22"/>
     </row>
-    <row r="140" ht="56" customHeight="1">
+    <row r="140" ht="138.71" customHeight="true">
       <c r="A140" s="0"/>
       <c r="B140" s="21"/>
       <c r="C140" s="22"/>
@@ -35173,7 +35173,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="61"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="43"/>
   <rowBreaks count="9" manualBreakCount="9">
     <brk id="14" max="16383" man="1"/>
     <brk id="28" max="16383" man="1"/>
